--- a/src/app/modules/dashboard/excel_files/delicious-whole-food-plant-based-diet-snack-hacks-1.xlsx
+++ b/src/app/modules/dashboard/excel_files/delicious-whole-food-plant-based-diet-snack-hacks-1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V57"/>
+  <dimension ref="A1:W57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,95 +446,100 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>recipe_id</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ingredients</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>instructions</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>nutritional</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>serving_size</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>prep_time</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>oils</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>whole_food_type</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>flavor</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>weight_and_muscle</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>kid_approved</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>no_weekend_prep</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>holiday_recipes</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>serving_temperature</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ratting</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>recipe_tips</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>prep</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>prep_time_note</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>prep_list</t>
         </is>
@@ -553,84 +558,89 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AVOCADO AND CHICKPEA SALAD</t>
+          <t>Avocado And Chickpea Salad</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>3583</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>['1 ripe avocado, mashed', '1 cup canned chickpeas, rinsed and mashed', '1 tbsp lemon juice', '1/4 tsp garlic powder', 'Salt and pepper to taste']</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>1. In a bowl, mash the avocado and chickpeas together.
 2. Add lemon juice, garlic powder, salt, and pepper.
 3. Mix well and serve with crackers or veggies.</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>{"calories": 240.0, "protein": 6.8, "carbs": 21.2, "fiber": 8.1, "fat": 14.5}</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>1-2 servings</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>10</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N2" t="b">
-        <v>0</v>
-      </c>
       <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" t="b">
         <v>1</v>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr">
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
         <is>
           <t>1. In a bowl, mash the avocado and chickpeas together.
 2. Add lemon juice, garlic powder, salt, and pepper.
 3. Mix well and serve with crackers or veggies.</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr">
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr">
         <is>
           <t>['In a bowl, mash the avocado and chickpeas together.', 'Add lemon juice, garlic powder, salt, and pepper.', 'Mix well and serve with crackers or veggies.']</t>
         </is>
@@ -649,15 +659,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CRISPY ROASTED CHICKPEAS</t>
+          <t>Crispy Roasted Chickpeas</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>3584</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>['1 can chickpeas, drained and rinsed', '1 tsp smoked paprika', '1/2 tsp garlic powder', '1/2 tsp cumin', 'Salt to taste']</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 400°F (200°C).
 2. Pat chickpeas dry with a paper towel.
@@ -665,61 +680,61 @@
 4. Spread chickpeas on a baking sheet and roast for 25-30 minutes until crispy.</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>{"calories": 180.0, "protein": 7.6, "carbs": 28.4, "fiber": 7.1, "fat": 3.2}</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>30</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N3" t="b">
-        <v>0</v>
-      </c>
       <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" t="b">
         <v>1</v>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr">
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 400°F (200°C).
 2. Pat chickpeas dry with a paper towel.
@@ -727,8 +742,8 @@
 4. Spread chickpeas on a baking sheet and roast for 25-30 minutes until crispy.</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr">
         <is>
           <t>['Preheat the oven to 400°F (200°C).', 'Pat chickpeas dry with a paper towel.', 'Toss chickpeas with paprika, garlic powder, cumin, and salt.', 'Spread chickpeas on a baking sheet and roast for 25-30 minutes until crispy.']</t>
         </is>
@@ -747,82 +762,87 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CARROT &amp; HUMMUS STICKS</t>
+          <t>Carrot &amp; Hummus Sticks</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>3585</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>['2 carrots, peeled and cut into sticks', '¼ cup hummus']</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>1. Peel and cut the carrots into sticks.
 2. Serve with hummus for dipping.</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>{"calories": 100.0, "protein": 2.0, "carbs": 12.0, "fiber": 4.0, "fat": 5.0}</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>5</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N4" t="b">
-        <v>0</v>
-      </c>
       <c r="O4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" t="b">
         <v>1</v>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr">
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
         <is>
           <t>1. Peel and cut the carrots into sticks.
 2. Serve with hummus for dipping.</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr">
         <is>
           <t>['Peel and cut the carrots into sticks.', 'Serve with hummus for dipping.']</t>
         </is>
@@ -841,84 +861,89 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CUCUMBER AND TOMATO BITES</t>
+          <t>Cucumber And Tomato Bites</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>3586</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>['1 cucumber, sliced', '1 tomato, diced', '1 tbsp fresh parsley, chopped', 'Salt and pepper to taste']</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>1. Slice cucumber into rounds.
 2. Top each slice with diced tomato, parsley, salt, and pepper.
 3. Serve immediately.</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>{"calories": 35.0, "protein": 1.0, "carbs": 7.0, "fiber": 2.0, "fat": 0.0}</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>5</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N5" t="b">
-        <v>0</v>
-      </c>
       <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" t="b">
         <v>1</v>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr">
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
         <is>
           <t>1. Slice cucumber into rounds.
 2. Top each slice with diced tomato, parsley, salt, and pepper.
 3. Serve immediately.</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr">
         <is>
           <t>['Slice cucumber into rounds.', 'Top each slice with diced tomato, parsley, salt, and pepper.', 'Serve immediately.']</t>
         </is>
@@ -937,84 +962,89 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VEGAN GUACAMOLE</t>
+          <t>Vegan Guacamole</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>3587</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>['2 ripe avocados', '¼ cup red onion, finely chopped', '1 small tomato, diced', '1 tbsp cilantro, chopped', '1 tbsp lime juice', 'Salt to taste']</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>1. Mash the avocados in a bowl.
 2. Add onion, tomato, cilantro, lime juice, and salt.
 3. Mix well and serve with tortilla chips or veggies.</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>{"calories": 160.0, "protein": 2.0, "carbs": 8.0, "fiber": 6.0, "fat": 14.0}</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>4 servings</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>10</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N6" t="b">
-        <v>0</v>
-      </c>
       <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" t="b">
         <v>1</v>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr">
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
         <is>
           <t>1. Mash the avocados in a bowl.
 2. Add onion, tomato, cilantro, lime juice, and salt.
 3. Mix well and serve with tortilla chips or veggies.</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr">
         <is>
           <t>['Mash the avocados in a bowl.', 'Add onion, tomato, cilantro, lime juice, and salt.', 'Mix well and serve with tortilla chips or veggies.']</t>
         </is>
@@ -1033,15 +1063,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BAKED SWEET POTATO FRIES</t>
+          <t>Baked Sweet Potato Fries</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>3588</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>['1 medium sweet potato', '½ tsp paprika', '½ tsp garlic powder', 'Salt and pepper to taste']</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 400°F (200°C).
 2. Slice the sweet potato into thin fries.
@@ -1049,61 +1084,61 @@
 4. Bake for 25-30 minutes, flipping halfway, until crispy.</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>{"calories": 120.0, "protein": 2.0, "carbs": 28.0, "fiber": 4.0, "fat": 0.0}</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>35</v>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L7" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N7" t="b">
-        <v>0</v>
-      </c>
       <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" t="b">
         <v>1</v>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr">
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 400°F (200°C).
 2. Slice the sweet potato into thin fries.
@@ -1111,8 +1146,8 @@
 4. Bake for 25-30 minutes, flipping halfway, until crispy.</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr">
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
         <is>
           <t>['Preheat the oven to 400°F (200°C).', 'Slice the sweet potato into thin fries.', 'Toss with paprika, garlic powder, salt, and pepper.', 'Bake for 25-30 minutes, flipping halfway, until crispy.']</t>
         </is>
@@ -1131,82 +1166,87 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VEGAN POPCORN</t>
+          <t>Vegan Popcorn</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>3589</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>['½ cup popcorn kernels', '¼ tsp sea salt']</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>1. Pop the popcorn kernels in an air- popper or on the stovetop with a dry pan.
 2. Sprinkle with sea salt and serve.</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>{"calories": 70.0, "protein": 2.0, "carbs": 14.0, "fiber": 3.0, "fat": 0.5}</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>4 servings</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>10</v>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N8" t="b">
-        <v>0</v>
-      </c>
       <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" t="b">
         <v>1</v>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr">
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
         <is>
           <t>1. Pop the popcorn kernels in an air- popper or on the stovetop with a dry pan.
 2. Sprinkle with sea salt and serve.</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
         <is>
           <t>['Pop the popcorn kernels in an air- popper or on the stovetop with a dry pan.', 'Sprinkle with sea salt and serve.']</t>
         </is>
@@ -1225,15 +1265,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ZUCCHINI CHIPS</t>
+          <t>Zucchini Chips</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>3590</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>['2 zucchini, thinly sliced', '1 tsp paprika', '½ tsp garlic powder', 'Salt to taste']</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 425°F (220°C).
 2. Arrange zucchini slices on a baking sheet.
@@ -1241,61 +1286,61 @@
 4. Bake for 20-25 minutes, flipping halfway through.</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>{"calories": 50.0, "protein": 2.0, "carbs": 10.0, "fiber": 2.0, "fat": 0.0}</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>25</v>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N9" t="b">
-        <v>0</v>
-      </c>
       <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
         <v>1</v>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr">
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 425°F (220°C).
 2. Arrange zucchini slices on a baking sheet.
@@ -1303,8 +1348,8 @@
 4. Bake for 20-25 minutes, flipping halfway through.</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr">
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
         <is>
           <t>['Preheat the oven to 425°F (220°C).', 'Arrange zucchini slices on a baking sheet.', 'Sprinkle with paprika, garlic powder, and salt.', 'Bake for 20-25 minutes, flipping halfway through.']</t>
         </is>
@@ -1323,84 +1368,89 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ROASTED PUMPKIN SEEDS</t>
+          <t>Roasted Pumpkin Seeds</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>3591</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>['1 cup pumpkin seeds', '1 tsp smoked paprika', '½ tsp garlic powder', 'Salt to taste']</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 375°F (190°C).
 2. Toss pumpkin seeds with paprika, garlic powder, and salt.
 3. Roast for 20-25 minutes, stirring halfway.</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>{"calories": 140.0, "protein": 7.0, "carbs": 5.0, "fiber": 2.0, "fat": 10.0}</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>25</v>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N10" t="b">
-        <v>0</v>
-      </c>
       <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
         <v>1</v>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr">
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 375°F (190°C).
 2. Toss pumpkin seeds with paprika, garlic powder, and salt.
 3. Roast for 20-25 minutes, stirring halfway.</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr">
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
         <is>
           <t>['Preheat the oven to 375°F (190°C).', 'Toss pumpkin seeds with paprika, garlic powder, and salt.', 'Roast for 20-25 minutes, stirring halfway.']</t>
         </is>
@@ -1419,82 +1469,87 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>VEGAN FRUIT SALAD</t>
+          <t>Vegan Fruit Salad</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>3592</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>['1 apple, diced', '1 orange, segmented', '½ cup grapes, halved', '½ cup strawberries, chopped', '1 tbsp lime juice']</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>1. Combine all fruits in a bowl.
 2. Drizzle with lime juice and toss gently before serving.</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>{"calories": 80.0, "protein": 1.0, "carbs": 21.0, "fiber": 3.0, "fat": 0.0}</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>5</v>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N11" t="b">
-        <v>0</v>
-      </c>
       <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
         <v>1</v>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr">
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
         <is>
           <t>1. Combine all fruits in a bowl.
 2. Drizzle with lime juice and toss gently before serving.</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr">
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
         <is>
           <t>['Combine all fruits in a bowl.', 'Drizzle with lime juice and toss gently before serving.']</t>
         </is>
@@ -1513,84 +1568,89 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>VEGAN APPLE NACHOS</t>
+          <t>Vegan Apple Nachos</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>3593</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>['1 apple, sliced thin', '2 tbsp peanut butter', '1 tbsp raisins', '1 tbsp chopped nuts (optional)']</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>1. Arrange apple slices on a plate.
 2. Drizzle with peanut butter and sprinkle with raisins and nuts.
 3. Serve immediately.</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>{"calories": 150.0, "protein": 4.0, "carbs": 20.0, "fiber": 4.0, "fat": 7.0}</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>5</v>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N12" t="b">
-        <v>0</v>
-      </c>
       <c r="O12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P12" t="b">
         <v>1</v>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr">
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
         <is>
           <t>1. Arrange apple slices on a plate.
 2. Drizzle with peanut butter and sprinkle with raisins and nuts.
 3. Serve immediately.</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr">
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
         <is>
           <t>['Arrange apple slices on a plate.', 'Drizzle with peanut butter and sprinkle with raisins and nuts.', 'Serve immediately.']</t>
         </is>
@@ -1609,84 +1669,89 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>VEGAN BANANA ICE CREAM</t>
+          <t>Vegan Banana Ice Cream</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>3594</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>['2 ripe bananas, frozen', '½ tsp vanilla extract', '1 tbsp almond milk (optional for creaminess)']</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>1. Blend the frozen bananas in a food processor until smooth and creamy.
 2. Add vanilla extract and almond milk (if needed) to get a creamy consistency.
 3. Serve immediately as soft-serve or freeze for 1-2 hours for a firmer texture.</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>{"calories": 105.0, "protein": 1.0, "carbs": 27.0, "fiber": 3.0, "fat": 0.0}</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>5</v>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>['desserts', 'oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L13" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N13" t="b">
-        <v>0</v>
-      </c>
       <c r="O13" t="b">
+        <v>0</v>
+      </c>
+      <c r="P13" t="b">
         <v>1</v>
       </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr">
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
         <is>
           <t>1. Blend the frozen bananas in a food processor until smooth and creamy.
 2. Add vanilla extract and almond milk (if needed) to get a creamy consistency.
 3. Serve immediately as soft-serve or freeze for 1-2 hours for a firmer texture.</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr">
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
         <is>
           <t>['Blend the frozen bananas in a food processor until smooth and creamy.', 'Add vanilla extract and almond milk (if needed) to get a creamy consistency.', 'Serve immediately as soft-serve or freeze for 1-2 hours for a firmer texture.']</t>
         </is>
@@ -1705,15 +1770,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>VEGAN TOFU BITES</t>
+          <t>Vegan Tofu Bites</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>3595</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>['½ block firm tofu', '1 tbsp soy sauce', '¼ tsp garlic powder', '¼ tsp smoked paprika', 'Salt and pepper to taste']</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 375°F (190°C).
 2. Press tofu to remove excess water, then cut into small cubes.
@@ -1721,61 +1791,61 @@
 4. Bake for 15-20 minutes until crispy, flipping halfway.</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>{"calories": 120.0, "protein": 11.0, "carbs": 5.0, "fiber": 1.0, "fat": 6.0}</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>20</v>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L14" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N14" t="b">
-        <v>0</v>
-      </c>
       <c r="O14" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" t="b">
         <v>1</v>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr">
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 375°F (190°C).
 2. Press tofu to remove excess water, then cut into small cubes.
@@ -1783,8 +1853,8 @@
 4. Bake for 15-20 minutes until crispy, flipping halfway.</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr">
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
         <is>
           <t>['Preheat the oven to 375°F (190°C).', 'Press tofu to remove excess water, then cut into small cubes.', 'Toss tofu cubes with soy sauce, garlic powder, smoked paprika, salt, and pepper.', 'Bake for 15-20 minutes until crispy, flipping halfway.']</t>
         </is>
@@ -1803,84 +1873,89 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CUCUMBER AND GUACAMOLE BITES</t>
+          <t>Cucumber And Guacamole Bites</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>3596</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>['1 cucumber, sliced into rounds', '¼ cup guacamole']</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>1. Slice the cucumber into rounds.
 2. Top each cucumber slice with a dollop of guacamole.
 3. Serve immediately.</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>{"calories": 90.0, "protein": 1.5, "carbs": 9.0, "fiber": 4.0, "fat": 6.0}</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>5</v>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L15" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N15" t="b">
-        <v>0</v>
-      </c>
       <c r="O15" t="b">
+        <v>0</v>
+      </c>
+      <c r="P15" t="b">
         <v>1</v>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr">
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
         <is>
           <t>1. Slice the cucumber into rounds.
 2. Top each cucumber slice with a dollop of guacamole.
 3. Serve immediately.</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr">
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
         <is>
           <t>['Slice the cucumber into rounds.', 'Top each cucumber slice with a dollop of guacamole.', 'Serve immediately.']</t>
         </is>
@@ -1899,82 +1974,87 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HOMEMADE TRAIL MIX</t>
+          <t>Homemade Trail Mix</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>3597</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>['¼ cup almonds', '¼ cup cashews', '¼ cup sunflower seeds', '¼ cup raisins', '¼ cup dark chocolate chips (optional)']</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>1. Mix all ingredients together in a bowl.
 2. Serve immediately or store in an airtight container for later.</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>{"calories": 210.0, "protein": 6.0, "carbs": 18.0, "fiber": 4.0, "fat": 13.0}</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>5</v>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L16" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N16" t="b">
-        <v>0</v>
-      </c>
       <c r="O16" t="b">
+        <v>0</v>
+      </c>
+      <c r="P16" t="b">
         <v>1</v>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr">
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
         <is>
           <t>1. Mix all ingredients together in a bowl.
 2. Serve immediately or store in an airtight container for later.</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr">
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
         <is>
           <t>['Mix all ingredients together in a bowl.', 'Serve immediately or store in an airtight container for later.']</t>
         </is>
@@ -1993,15 +2073,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CHIA SEED CRACKERS</t>
+          <t>Chia Seed Crackers</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>3598</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>['1 cup ground flaxseeds', '½ cup chia seeds', '¼ tsp sea salt', '½ cup water']</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>1. Mix the ground flaxseeds, chia seeds, and salt in a bowl.
 2. Add water and stir until a thick dough forms.
@@ -2009,61 +2094,61 @@
 4. Cut into squares and bake at 350°F (175°C) for 15-20 minutes, or until crispy.</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>{"calories": 210.0, "protein": 7.0, "carbs": 9.0, "fiber": 7.0, "fat": 14.0}</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>10</v>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L17" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N17" t="b">
-        <v>0</v>
-      </c>
       <c r="O17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P17" t="b">
         <v>1</v>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr">
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
         <is>
           <t>1. Mix the ground flaxseeds, chia seeds, and salt in a bowl.
 2. Add water and stir until a thick dough forms.
@@ -2071,8 +2156,8 @@
 4. Cut into squares and bake at 350°F (175°C) for 15-20 minutes, or until crispy.</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr">
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr">
         <is>
           <t>['Mix the ground flaxseeds, chia seeds, and salt in a bowl.', 'Add water and stir until a thick dough forms.', 'Roll the dough out between two pieces of parchment paper to about ⅛ inch thick.', 'Cut into squares and bake at 350°F (175°C) for 15-20 minutes, or until crispy.']</t>
         </is>
@@ -2091,84 +2176,89 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TOMATO &amp; BASIL BRUSCHETTA</t>
+          <t>Tomato &amp; Basil Bruschetta</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>3599</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>['1 baguette, sliced', '2 tomatoes, diced', '2 tbsp fresh basil, chopped', '1 tbsp balsamic vinegar', 'Salt and pepper to taste']</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>1. Toast baguette slices in the oven at 350°F (175°C) for about 5 minutes.
 2. In a bowl, mix tomatoes, basil, balsamic vinegar, salt, and pepper.
 3. Top the toasted baguette slices with the tomato mixture and serve.</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>{"calories": 180.0, "protein": 5.0, "carbs": 36.0, "fiber": 3.0, "fat": 1.0}</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>4 servings</t>
         </is>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>10</v>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L18" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N18" t="b">
-        <v>0</v>
-      </c>
       <c r="O18" t="b">
+        <v>0</v>
+      </c>
+      <c r="P18" t="b">
         <v>1</v>
       </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr">
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
         <is>
           <t>1. Toast baguette slices in the oven at 350°F (175°C) for about 5 minutes.
 2. In a bowl, mix tomatoes, basil, balsamic vinegar, salt, and pepper.
 3. Top the toasted baguette slices with the tomato mixture and serve.</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr">
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
         <is>
           <t>['Toast baguette slices in the oven at 350°F (175°C) for about 5 minutes.', 'In a bowl, mix tomatoes, basil, balsamic vinegar, salt, and pepper.', 'Top the toasted baguette slices with the tomato mixture and serve.']</t>
         </is>
@@ -2187,15 +2277,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>VEGAN CHEESE STUFFED MUSHROOMS</t>
+          <t>Vegan Cheese Stuffed Mushrooms</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>3600</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>['6 large mushroom caps', '¼ cup nutritional yeast', '¼ cup breadcrumbs', '1 tbsp chopped parsley', 'Salt and pepper to taste']</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 375°F (190°C).
 2. Remove the stems from the mushrooms and set aside.
@@ -2203,61 +2298,61 @@
 4. Stuff the mushroom caps with the mixture and bake for 15-20 minutes.</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>{"calories": 120.0, "protein": 6.0, "carbs": 18.0, "fiber": 4.0, "fat": 2.0}</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>20</v>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N19" t="b">
-        <v>0</v>
-      </c>
       <c r="O19" t="b">
+        <v>0</v>
+      </c>
+      <c r="P19" t="b">
         <v>1</v>
       </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr">
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr">
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 375°F (190°C).
 2. Remove the stems from the mushrooms and set aside.
@@ -2265,8 +2360,8 @@
 4. Stuff the mushroom caps with the mixture and bake for 15-20 minutes.</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr">
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr">
         <is>
           <t>['Preheat the oven to 375°F (190°C).', 'Remove the stems from the mushrooms and set aside.', 'Mix nutritional yeast, breadcrumbs, parsley, salt, and pepper.', 'Stuff the mushroom caps with the mixture and bake for 15-20 minutes.']</t>
         </is>
@@ -2285,82 +2380,87 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CUCUMBER SALSA</t>
+          <t>Cucumber Salsa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>3601</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>['1 cucumber, diced', '1 tomato, diced', '1 tbsp fresh cilantro, chopped', '1 tbsp lime juice', 'Salt to taste']</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>1. Combine all ingredients in a bowl and toss well.
 2. Serve with tortilla chips or as a topping for other dishes.</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>{"calories": 35.0, "protein": 1.0, "carbs": 8.0, "fiber": 2.0, "fat": 0.0}</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>5</v>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L20" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N20" t="b">
-        <v>0</v>
-      </c>
       <c r="O20" t="b">
+        <v>0</v>
+      </c>
+      <c r="P20" t="b">
         <v>1</v>
       </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr">
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr">
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
         <is>
           <t>1. Combine all ingredients in a bowl and toss well.
 2. Serve with tortilla chips or as a topping for other dishes.</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr">
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr">
         <is>
           <t>['Combine all ingredients in a bowl and toss well.', 'Serve with tortilla chips or as a topping for other dishes.']</t>
         </is>
@@ -2379,84 +2479,89 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>VEGAN PEANUT BUTTER &amp; JELLY BITES</t>
+          <t>Vegan Peanut Butter &amp; Jelly Bites</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>3602</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>['6 graham crackers, broken into pieces', '2 tbsp peanut butter', '2 tbsp fruit jam (strawberry, raspberry, etc.)']</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>1. Spread peanut butter on half of the graham cracker pieces.
 2. Spread jam on the other half.
 3. Sandwich the cracker pieces together and serve.</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>{"calories": 190.0, "protein": 5.0, "carbs": 30.0, "fiber": 2.0, "fat": 7.0}</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>5</v>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L21" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N21" t="b">
-        <v>0</v>
-      </c>
       <c r="O21" t="b">
+        <v>0</v>
+      </c>
+      <c r="P21" t="b">
         <v>1</v>
       </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr">
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr">
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
         <is>
           <t>1. Spread peanut butter on half of the graham cracker pieces.
 2. Spread jam on the other half.
 3. Sandwich the cracker pieces together and serve.</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr">
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr">
         <is>
           <t>['Spread peanut butter on half of the graham cracker pieces.', 'Spread jam on the other half.', 'Sandwich the cracker pieces together and serve.']</t>
         </is>
@@ -2475,84 +2580,89 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>VEGAN APPLE NACHOS</t>
+          <t>Vegan Apple Nachos</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>3603</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>['1 apple, thinly sliced', '2 tbsp peanut butter', '1 tbsp raisins', '1 tbsp sunflower seeds']</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>1. Arrange apple slices on a plate.
 2. Drizzle with peanut butter and sprinkle with raisins and sunflower seeds.
 3. Serve immediately.</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>{"calories": 210.0, "protein": 5.0, "carbs": 30.0, "fiber": 6.0, "fat": 9.0}</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>5</v>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N22" t="b">
-        <v>0</v>
-      </c>
       <c r="O22" t="b">
+        <v>0</v>
+      </c>
+      <c r="P22" t="b">
         <v>1</v>
       </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr">
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
         <is>
           <t>1. Arrange apple slices on a plate.
 2. Drizzle with peanut butter and sprinkle with raisins and sunflower seeds.
 3. Serve immediately.</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr">
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr">
         <is>
           <t>['Arrange apple slices on a plate.', 'Drizzle with peanut butter and sprinkle with raisins and sunflower seeds.', 'Serve immediately.']</t>
         </is>
@@ -2571,82 +2681,87 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>VEGAN PESTO DIP</t>
+          <t>Vegan Pesto Dip</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>3604</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>['1 cup fresh basil', '¼ cup sunflower seeds', '1 tbsp nutritional yeast', '1 tbsp lemon juice', '¼ cup water', 'Salt and pepper to taste']</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>1. Blend all ingredients in a food processor until smooth.
 2. Serve as a dip with veggie sticks or crackers.</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>{"calories": 140.0, "protein": 5.0, "carbs": 6.0, "fiber": 2.0, "fat": 10.0}</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>5</v>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N23" t="b">
-        <v>0</v>
-      </c>
       <c r="O23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P23" t="b">
         <v>1</v>
       </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr">
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
         <is>
           <t>1. Blend all ingredients in a food processor until smooth.
 2. Serve as a dip with veggie sticks or crackers.</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr">
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr">
         <is>
           <t>['Blend all ingredients in a food processor until smooth.', 'Serve as a dip with veggie sticks or crackers.']</t>
         </is>
@@ -2665,84 +2780,89 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>VEGAN STUFFED AVOCADOS</t>
+          <t>Vegan Stuffed Avocados</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>3605</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>['2 ripe avocados, halved and pitted', '¼ cup cherry tomatoes, chopped', '2 tbsp red onion, finely diced', '1 tbsp lime juice', 'Salt and pepper to taste']</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>1. Scoop out a bit of the avocado to create space for stuffing.
 2. Mix the tomato, onion, lime juice, salt, and pepper in a bowl.
 3. Fill the avocado halves with the mixture and serve immediately.</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>{"calories": 210.0, "protein": 3.0, "carbs": 12.0, "fiber": 7.0, "fat": 17.0}</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>5</v>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L24" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N24" t="b">
-        <v>0</v>
-      </c>
       <c r="O24" t="b">
+        <v>0</v>
+      </c>
+      <c r="P24" t="b">
         <v>1</v>
       </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr">
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr">
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
         <is>
           <t>1. Scoop out a bit of the avocado to create space for stuffing.
 2. Mix the tomato, onion, lime juice, salt, and pepper in a bowl.
 3. Fill the avocado halves with the mixture and serve immediately.</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr">
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr">
         <is>
           <t>['Scoop out a bit of the avocado to create space for stuffing.', 'Mix the tomato, onion, lime juice, salt, and pepper in a bowl.', 'Fill the avocado halves with the mixture and serve immediately.']</t>
         </is>
@@ -2761,84 +2881,89 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ROASTED BRUSSELS SPROUTS CHIPS</t>
+          <t>Roasted Brussels Sprouts Chips</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>3606</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>['1 lb Brussels sprouts, trimmed and halved', '1 tsp smoked paprika', 'Salt and pepper to taste']</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 400°F (200°C).
 2. Toss Brussels sprouts with paprika, salt, and pepper.
 3. Roast for 20-25 minutes, flipping halfway, until crispy.</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>{"calories": 120.0, "protein": 5.0, "carbs": 20.0, "fiber": 6.0, "fat": 2.0}</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>25</v>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L25" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N25" t="b">
-        <v>0</v>
-      </c>
       <c r="O25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P25" t="b">
         <v>1</v>
       </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr">
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 400°F (200°C).
 2. Toss Brussels sprouts with paprika, salt, and pepper.
 3. Roast for 20-25 minutes, flipping halfway, until crispy.</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr">
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr">
         <is>
           <t>['Preheat the oven to 400°F (200°C).', 'Toss Brussels sprouts with paprika, salt, and pepper.', 'Roast for 20-25 minutes, flipping halfway, until crispy.']</t>
         </is>
@@ -2857,84 +2982,89 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>VEGAN MOZZARELLA STICKS</t>
+          <t>Vegan Mozzarella Sticks</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>3607</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>['1 block firm tofu, cut into strips', '¼ cup nutritional yeast', '¼ cup breadcrumbs', '1 tbsp garlic powder', 'Salt and pepper to taste']</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 375°F (190°C).
 2. Coat tofu strips with nutritional yeast, breadcrumbs, garlic powder, salt, and pepper.
 3. Bake for 20 minutes, flipping halfway, until crispy.</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>{"calories": 180.0, "protein": 14.0, "carbs": 12.0, "fiber": 3.0, "fat": 7.0}</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>15</v>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L26" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N26" t="b">
-        <v>0</v>
-      </c>
       <c r="O26" t="b">
+        <v>0</v>
+      </c>
+      <c r="P26" t="b">
         <v>1</v>
       </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr">
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr">
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 375°F (190°C).
 2. Coat tofu strips with nutritional yeast, breadcrumbs, garlic powder, salt, and pepper.
 3. Bake for 20 minutes, flipping halfway, until crispy.</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr">
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr">
         <is>
           <t>['Preheat the oven to 375°F (190°C).', 'Coat tofu strips with nutritional yeast, breadcrumbs, garlic powder, salt, and pepper.', 'Bake for 20 minutes, flipping halfway, until crispy.']</t>
         </is>
@@ -2953,82 +3083,87 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>VEGAN SWEET POTATO HUMMUS</t>
+          <t>Vegan Sweet Potato Hummus</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>3608</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>['1 small sweet potato, roasted and peeled', '½ cup tahini', '1 tbsp lemon juice', '1 clove garlic, minced', 'Salt and pepper to taste']</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>1. Blend all ingredients in a food processor until smooth.
 2. Serve with pita or veggies for dipping.</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>{"calories": 180.0, "protein": 6.0, "carbs": 22.0, "fiber": 4.0, "fat": 10.0}</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>10</v>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L27" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N27" t="b">
-        <v>0</v>
-      </c>
       <c r="O27" t="b">
+        <v>0</v>
+      </c>
+      <c r="P27" t="b">
         <v>1</v>
       </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr">
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr">
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
         <is>
           <t>1. Blend all ingredients in a food processor until smooth.
 2. Serve with pita or veggies for dipping.</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr">
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr">
         <is>
           <t>['Blend all ingredients in a food processor until smooth.', 'Serve with pita or veggies for dipping.']</t>
         </is>
@@ -3047,84 +3182,89 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SPICY ROASTED EDAMAME</t>
+          <t>Spicy Roasted Edamame</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>3609</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>['1 cup shelled edamame', '½ tsp smoked paprika', '½ tsp garlic powder', '¼ tsp chili flakes']</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F (190°C).
 2. Toss edamame with seasonings.
 3. Bake for 15-20 minutes, flipping halfway.</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>{"calories": 140.0, "protein": 12.0, "carbs": 14.0, "fiber": 5.0, "fat": 4.0}</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>20</v>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N28" t="b">
-        <v>0</v>
-      </c>
       <c r="O28" t="b">
+        <v>0</v>
+      </c>
+      <c r="P28" t="b">
         <v>1</v>
       </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr">
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F (190°C).
 2. Toss edamame with seasonings.
 3. Bake for 15-20 minutes, flipping halfway.</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr">
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr">
         <is>
           <t>['Preheat oven to 375°F (190°C).', 'Toss edamame with seasonings.', 'Bake for 15-20 minutes, flipping halfway.']</t>
         </is>
@@ -3143,84 +3283,89 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BAKED CINNAMON APPLE CHIPS</t>
+          <t>Baked Cinnamon Apple Chips</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>3610</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>['1 apple, thinly sliced', '½ tsp cinnamon']</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>1. Preheat oven to 250°F (120°C).
 2. Arrange apple slices on a baking sheet.
 3. Sprinkle with cinnamon and bake for 30-40 minutes, flipping halfway.</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>{"calories": 90.0, "protein": 0.5, "carbs": 24.0, "fiber": 4.0, "fat": 0.0}</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>40</v>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L29" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N29" t="b">
-        <v>0</v>
-      </c>
       <c r="O29" t="b">
+        <v>0</v>
+      </c>
+      <c r="P29" t="b">
         <v>1</v>
       </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr">
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
         <is>
           <t>1. Preheat oven to 250°F (120°C).
 2. Arrange apple slices on a baking sheet.
 3. Sprinkle with cinnamon and bake for 30-40 minutes, flipping halfway.</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr">
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr">
         <is>
           <t>['Preheat oven to 250°F (120°C).', 'Arrange apple slices on a baking sheet.', 'Sprinkle with cinnamon and bake for 30-40 minutes, flipping halfway.']</t>
         </is>
@@ -3239,84 +3384,89 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MANGO &amp; COCONUT CHIA PUDDING</t>
+          <t>Mango &amp; Coconut Chia Pudding</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>3611</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>['1 cup almond milk', '2 tbsp chia seeds', '½ cup mango puree', '1 tbsp shredded coconut']</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>1. Mix almond milk and chia seeds in a jar.
 2. Let sit in the fridge for 4 hours.
 3. Stir in mango puree and top with shredded coconut.</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>{"calories": 170.0, "protein": 4.0, "carbs": 25.0, "fiber": 5.0, "fat": 6.0}</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>5</v>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t>['desserts', 'oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L30" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N30" t="b">
-        <v>0</v>
-      </c>
       <c r="O30" t="b">
+        <v>0</v>
+      </c>
+      <c r="P30" t="b">
         <v>1</v>
       </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr">
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr">
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
         <is>
           <t>1. Mix almond milk and chia seeds in a jar.
 2. Let sit in the fridge for 4 hours.
 3. Stir in mango puree and top with shredded coconut.</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr">
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr">
         <is>
           <t>['Mix almond milk and chia seeds in a jar.', 'Let sit in the fridge for 4 hours.', 'Stir in mango puree and top with shredded coconut.']</t>
         </is>
@@ -3335,84 +3485,89 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ROASTED SPICED CHICKPEAS</t>
+          <t>Roasted Spiced Chickpeas</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>3612</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>['1 can chickpeas, drained and rinsed', '½ tsp cumin', '½ tsp smoked paprika']</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>1. Preheat oven to 400°F (200°C).
 2. Toss chickpeas with spices.
 3. Bake for 25-30 minutes, flipping halfway.</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>{"calories": 140.0, "protein": 6.0, "carbs": 23.0, "fiber": 6.0, "fat": 2.0}</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>30</v>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N31" t="b">
-        <v>0</v>
-      </c>
       <c r="O31" t="b">
+        <v>0</v>
+      </c>
+      <c r="P31" t="b">
         <v>1</v>
       </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr">
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr">
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
         <is>
           <t>1. Preheat oven to 400°F (200°C).
 2. Toss chickpeas with spices.
 3. Bake for 25-30 minutes, flipping halfway.</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr">
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr">
         <is>
           <t>['Preheat oven to 400°F (200°C).', 'Toss chickpeas with spices.', 'Bake for 25-30 minutes, flipping halfway.']</t>
         </is>
@@ -3431,82 +3586,87 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PEANUT BUTTER STUFFED CELERY</t>
+          <t>Peanut Butter Stuffed Celery</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>3613</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>['2 celery stalks, cut into sticks', '2 tbsp peanut butter', '1 tbsp raisins']</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>1. Fill celery sticks with peanut butter.
 2. Top with raisins and serve.</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>{"calories": 150.0, "protein": 5.0, "carbs": 12.0, "fiber": 3.0, "fat": 9.0}</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>5</v>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L32" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N32" t="b">
-        <v>0</v>
-      </c>
       <c r="O32" t="b">
+        <v>0</v>
+      </c>
+      <c r="P32" t="b">
         <v>1</v>
       </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr">
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr">
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
         <is>
           <t>1. Fill celery sticks with peanut butter.
 2. Top with raisins and serve.</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr">
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr">
         <is>
           <t>['Fill celery sticks with peanut butter.', 'Top with raisins and serve.']</t>
         </is>
@@ -3525,80 +3685,85 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BLUEBERRY ALMOND SNACK MIX</t>
+          <t>Blueberry Almond Snack Mix</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>3614</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>['¼ cup dried blueberries', '¼ cup almonds', '2 tbsp pumpkin seeds']</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>1. Mix all ingredients together in a bowl.</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>{"calories": 180.0, "protein": 5.0, "carbs": 20.0, "fiber": 4.0, "fat": 9.0}</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>5</v>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L33" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N33" t="b">
-        <v>0</v>
-      </c>
       <c r="O33" t="b">
+        <v>0</v>
+      </c>
+      <c r="P33" t="b">
         <v>1</v>
       </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr">
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr">
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
         <is>
           <t>1. Mix all ingredients together in a bowl.</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr">
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
         <is>
           <t>['Mix all ingredients together in a bowl.']</t>
         </is>
@@ -3617,82 +3782,87 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FROZEN GRAPES</t>
+          <t>Frozen Grapes</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>3615</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>['1 cup grapes']</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>1. Place grapes on a tray and freeze for 2 hours.
 2. Enjoy as a refreshing frozen snack.</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>{"calories": 55.0, "protein": 0.5, "carbs": 14.0, "fiber": 1.0, "fat": 0.0}</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>5</v>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t>['desserts', 'oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L34" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N34" t="b">
-        <v>0</v>
-      </c>
       <c r="O34" t="b">
+        <v>0</v>
+      </c>
+      <c r="P34" t="b">
         <v>1</v>
       </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr">
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr">
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
         <is>
           <t>1. Place grapes on a tray and freeze for 2 hours.
 2. Enjoy as a refreshing frozen snack.</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr">
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr">
         <is>
           <t>['Place grapes on a tray and freeze for 2 hours.', 'Enjoy as a refreshing frozen snack.']</t>
         </is>
@@ -3711,82 +3881,87 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EDAMAME &amp; SEA SALT</t>
+          <t>Edamame &amp; Sea Salt</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>3616</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>['1 cup cooked edamame', '¼ tsp sea salt']</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>1. Toss edamame with sea salt.
 2. Serve immediately.</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>{"calories": 95.0, "protein": 8.0, "carbs": 10.0, "fiber": 4.0, "fat": 3.0}</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>5</v>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L35" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N35" t="b">
-        <v>0</v>
-      </c>
       <c r="O35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P35" t="b">
         <v>1</v>
       </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr">
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr">
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
         <is>
           <t>1. Toss edamame with sea salt.
 2. Serve immediately.</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr">
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr">
         <is>
           <t>['Toss edamame with sea salt.', 'Serve immediately.']</t>
         </is>
@@ -3805,80 +3980,85 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SPICY CUCUMBER STICKS</t>
+          <t>Spicy Cucumber Sticks</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>3617</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>['1 cucumber, sliced into sticks', '½ tsp chili powder', '1 tsp lime juice']</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>1. Toss cucumber sticks with chili powder and lime juice.</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>{"calories": 15.0, "protein": 0.5, "carbs": 4.0, "fiber": 1.0, "fat": 0.0}</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>5</v>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L36" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N36" t="b">
-        <v>0</v>
-      </c>
       <c r="O36" t="b">
+        <v>0</v>
+      </c>
+      <c r="P36" t="b">
         <v>1</v>
       </c>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr">
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr">
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
         <is>
           <t>1. Toss cucumber sticks with chili powder and lime juice.</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr">
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr">
         <is>
           <t>['Toss cucumber sticks with chili powder and lime juice.']</t>
         </is>
@@ -3897,84 +4077,89 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ROASTED CAULIFLOWER BITES</t>
+          <t>Roasted Cauliflower Bites</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>3618</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>['2 cups cauliflower florets', '1 tsp smoked paprika', '½ tsp garlic powder', 'Salt to taste']</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 400°F (200°C).
 2. Toss cauliflower florets with smoked paprika, garlic powder, and salt.
 3. Spread on a baking sheet and roast for 25 minutes, flipping halfway.</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>{"calories": 70.0, "protein": 3.0, "carbs": 12.0, "fiber": 4.0, "fat": 0.5}</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>30</v>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L37" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N37" t="b">
-        <v>0</v>
-      </c>
       <c r="O37" t="b">
+        <v>0</v>
+      </c>
+      <c r="P37" t="b">
         <v>1</v>
       </c>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr">
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr">
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 400°F (200°C).
 2. Toss cauliflower florets with smoked paprika, garlic powder, and salt.
 3. Spread on a baking sheet and roast for 25 minutes, flipping halfway.</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr">
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr">
         <is>
           <t>['Preheat the oven to 400°F (200°C).', 'Toss cauliflower florets with smoked paprika, garlic powder, and salt.', 'Spread on a baking sheet and roast for 25 minutes, flipping halfway.']</t>
         </is>
@@ -3993,84 +4178,89 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>VEGAN CHOCOLATE-DIPPED BANANAS</t>
+          <t>Vegan Chocolate-Dipped Bananas</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>3619</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>['1 banana, sliced into chunks', '¼ cup vegan chocolate chips, melted', '1 tbsp shredded coconut (optional)']</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>1. Dip banana chunks in melted chocolate.
 2. Sprinkle with shredded coconut if desired.
 3. Freeze for 30 minutes before serving.</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>{"calories": 145.0, "protein": 1.5, "carbs": 28.0, "fiber": 3.0, "fat": 4.5}</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
         <v>10</v>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t>['desserts', 'oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L38" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N38" t="b">
-        <v>0</v>
-      </c>
       <c r="O38" t="b">
+        <v>0</v>
+      </c>
+      <c r="P38" t="b">
         <v>1</v>
       </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr">
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr">
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
         <is>
           <t>1. Dip banana chunks in melted chocolate.
 2. Sprinkle with shredded coconut if desired.
 3. Freeze for 30 minutes before serving.</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr">
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr">
         <is>
           <t>['Dip banana chunks in melted chocolate.', 'Sprinkle with shredded coconut if desired.', 'Freeze for 30 minutes before serving.']</t>
         </is>
@@ -4089,82 +4279,87 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CARROT AND CUCUMBER STICKS WITH MUSTARD</t>
+          <t>Carrot And Cucumber Sticks With Mustard</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>3620</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>['1 carrot, sliced into sticks', '1 cucumber, sliced into sticks', '2 tbsp Dijon mustard']</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>1. Arrange carrot and cucumber sticks on a plate.
 2. Serve with Dijon mustard for dipping.</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>{"calories": 45.0, "protein": 1.0, "carbs": 10.0, "fiber": 2.0, "fat": 0.3}</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>5</v>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L39" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N39" t="b">
-        <v>0</v>
-      </c>
       <c r="O39" t="b">
+        <v>0</v>
+      </c>
+      <c r="P39" t="b">
         <v>1</v>
       </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr">
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr">
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
         <is>
           <t>1. Arrange carrot and cucumber sticks on a plate.
 2. Serve with Dijon mustard for dipping.</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr">
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr">
         <is>
           <t>['Arrange carrot and cucumber sticks on a plate.', 'Serve with Dijon mustard for dipping.']</t>
         </is>
@@ -4183,84 +4378,89 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SWEET POTATO ROUNDS WITH GUACAMOLE</t>
+          <t>Sweet Potato Rounds With Guacamole</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>3621</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>['1 medium sweet potato, sliced into rounds', '¼ cup guacamole']</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 375°F (190°C).
 2. Bake sweet potato rounds for 20 minutes, flipping halfway.
 3. Top with guacamole and serve.</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>{"calories": 165.0, "protein": 2.5, "carbs": 28.0, "fiber": 5.0, "fat": 6.0}</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>25</v>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L40" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N40" t="b">
-        <v>0</v>
-      </c>
       <c r="O40" t="b">
+        <v>0</v>
+      </c>
+      <c r="P40" t="b">
         <v>1</v>
       </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr">
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr">
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 375°F (190°C).
 2. Bake sweet potato rounds for 20 minutes, flipping halfway.
 3. Top with guacamole and serve.</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr">
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr">
         <is>
           <t>['Preheat the oven to 375°F (190°C).', 'Bake sweet potato rounds for 20 minutes, flipping halfway.', 'Top with guacamole and serve.']</t>
         </is>
@@ -4279,84 +4479,89 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>KALE CHIPS WITH NUTRITIONAL YEAST</t>
+          <t>Kale Chips With Nutritional Yeast</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>3622</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>['4 cups kale leaves, torn into pieces', '1 tbsp nutritional yeast', '½ tsp garlic powder', 'Salt to taste']</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 300°F (150°C).
 2. Toss kale with nutritional yeast, garlic powder, and salt.
 3. Spread on a baking sheet and bake for 15-20 minutes until crispy.</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>{"calories": 40.0, "protein": 3.0, "carbs": 6.0, "fiber": 2.0, "fat": 0.5}</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>20</v>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L41" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N41" t="b">
-        <v>0</v>
-      </c>
       <c r="O41" t="b">
+        <v>0</v>
+      </c>
+      <c r="P41" t="b">
         <v>1</v>
       </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr">
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr">
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 300°F (150°C).
 2. Toss kale with nutritional yeast, garlic powder, and salt.
 3. Spread on a baking sheet and bake for 15-20 minutes until crispy.</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr">
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr">
         <is>
           <t>['Preheat the oven to 300°F (150°C).', 'Toss kale with nutritional yeast, garlic powder, and salt.', 'Spread on a baking sheet and bake for 15-20 minutes until crispy.']</t>
         </is>
@@ -4375,82 +4580,87 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>TROPICAL FRUIT SALAD</t>
+          <t>Tropical Fruit Salad</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t>3623</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>['½ cup diced pineapple', '½ cup diced mango', '¼ cup pomegranate seeds', '1 tsp lime juice']</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>1. Combine all ingredients in a bowl.
 2. Toss gently and serve chilled.</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>{"calories": 80.0, "protein": 1.0, "carbs": 20.0, "fiber": 3.0, "fat": 0.2}</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
         <v>5</v>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t>['desserts', 'oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N42" t="b">
-        <v>0</v>
-      </c>
       <c r="O42" t="b">
+        <v>0</v>
+      </c>
+      <c r="P42" t="b">
         <v>1</v>
       </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr">
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr">
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
         <is>
           <t>1. Combine all ingredients in a bowl.
 2. Toss gently and serve chilled.</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr">
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr">
         <is>
           <t>['Combine all ingredients in a bowl.', 'Toss gently and serve chilled.']</t>
         </is>
@@ -4469,82 +4679,87 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>STUFFED MINI BELL PEPPERS</t>
+          <t>Stuffed Mini Bell Peppers</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t>3624</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>['8 mini bell peppers, halved and deseeded', '½ cup hummus', '2 tbsp chopped parsley']</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>1. Fill each mini bell pepper half with hummus.
 2. Sprinkle with chopped parsley and serve immediately.</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>{"calories": 65.0, "protein": 3.0, "carbs": 9.0, "fiber": 3.0, "fat": 2.5}</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>4 servings</t>
         </is>
       </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
         <v>10</v>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L43" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N43" t="b">
-        <v>0</v>
-      </c>
       <c r="O43" t="b">
+        <v>0</v>
+      </c>
+      <c r="P43" t="b">
         <v>1</v>
       </c>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr">
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr">
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr">
         <is>
           <t>1. Fill each mini bell pepper half with hummus.
 2. Sprinkle with chopped parsley and serve immediately.</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr">
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr">
         <is>
           <t>['Fill each mini bell pepper half with hummus.', 'Sprinkle with chopped parsley and serve immediately.']</t>
         </is>
@@ -4563,84 +4778,89 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CUCUMBER SUSHI ROLLS</t>
+          <t>Cucumber Sushi Rolls</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t>3625</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>['1 cucumber, sliced into thin strips lengthwise', '1 carrot, julienned', '1 avocado, sliced', '2 tbsp tahini']</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>1. Spread a thin layer of tahini onto each cucumber slice.
 2. Add julienned carrots and avocado slices.
 3. Roll tightly and secure with a toothpick.</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>{"calories": 120.0, "protein": 3.0, "carbs": 8.0, "fiber": 4.0, "fat": 8.0}</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
         <v>10</v>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N44" t="b">
-        <v>0</v>
-      </c>
       <c r="O44" t="b">
+        <v>0</v>
+      </c>
+      <c r="P44" t="b">
         <v>1</v>
       </c>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr">
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr">
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr">
         <is>
           <t>1. Spread a thin layer of tahini onto each cucumber slice.
 2. Add julienned carrots and avocado slices.
 3. Roll tightly and secure with a toothpick.</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr">
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr">
         <is>
           <t>['Spread a thin layer of tahini onto each cucumber slice.', 'Add julienned carrots and avocado slices.', 'Roll tightly and secure with a toothpick.']</t>
         </is>
@@ -4659,15 +4879,20 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ZUCCHINI PIZZA BITES</t>
+          <t>Zucchini Pizza Bites</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>3626</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>['1 zucchini, sliced into rounds', '¼ cup marinara sauce', '2 tbsp nutritional yeast', '1 tsp Italian seasoning']</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 400°F (200°C).
 2. Place zucchini rounds on a baking sheet and top with marinara sauce.
@@ -4675,61 +4900,61 @@
 4. Bake for 10-12 minutes.</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>{"calories": 65.0, "protein": 3.0, "carbs": 10.0, "fiber": 3.0, "fat": 1.0}</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
         <v>15</v>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N45" t="b">
-        <v>0</v>
-      </c>
       <c r="O45" t="b">
+        <v>0</v>
+      </c>
+      <c r="P45" t="b">
         <v>1</v>
       </c>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr">
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr">
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 400°F (200°C).
 2. Place zucchini rounds on a baking sheet and top with marinara sauce.
@@ -4737,8 +4962,8 @@
 4. Bake for 10-12 minutes.</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr">
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr">
         <is>
           <t>['Preheat the oven to 400°F (200°C).', 'Place zucchini rounds on a baking sheet and top with marinara sauce.', 'Sprinkle with nutritional yeast and Italian seasoning.', 'Bake for 10-12 minutes.']</t>
         </is>
@@ -4757,82 +4982,87 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>VEGAN FRUIT DIP</t>
+          <t>Vegan Fruit Dip</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>3627</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>['½ cup unsweetened coconut yogurt', '1 tbsp maple syrup', '1 tsp vanilla extract']</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>1. Combine coconut yogurt, maple syrup, and vanilla extract in a bowl.
 2. Mix well and serve with fresh fruit for dipping.</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>{"calories": 70.0, "protein": 1.0, "carbs": 12.0, "fiber": 0.5, "fat": 2.0}</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
         <v>5</v>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N46" t="b">
-        <v>0</v>
-      </c>
       <c r="O46" t="b">
+        <v>0</v>
+      </c>
+      <c r="P46" t="b">
         <v>1</v>
       </c>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr">
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr">
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
         <is>
           <t>1. Combine coconut yogurt, maple syrup, and vanilla extract in a bowl.
 2. Mix well and serve with fresh fruit for dipping.</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr">
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr">
         <is>
           <t>['Combine coconut yogurt, maple syrup, and vanilla extract in a bowl.', 'Mix well and serve with fresh fruit for dipping.']</t>
         </is>
@@ -4851,84 +5081,89 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CARROT AND BEET CHIPS</t>
+          <t>Carrot And Beet Chips</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t>3628</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>['2 carrots, thinly sliced', '1 beet, thinly sliced', '½ tsp smoked paprika']</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 375°F (190°C).
 2. Arrange carrot and beet slices on a baking sheet.
 3. Sprinkle with smoked paprika and bake for 20-25 minutes, flipping halfway.</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>{"calories": 50.0, "protein": 1.0, "carbs": 12.0, "fiber": 3.0, "fat": 0.0}</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H47" t="n">
+      <c r="I47" t="n">
         <v>25</v>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L47" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N47" t="b">
-        <v>0</v>
-      </c>
       <c r="O47" t="b">
+        <v>0</v>
+      </c>
+      <c r="P47" t="b">
         <v>1</v>
       </c>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr">
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr">
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 375°F (190°C).
 2. Arrange carrot and beet slices on a baking sheet.
 3. Sprinkle with smoked paprika and bake for 20-25 minutes, flipping halfway.</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr">
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr">
         <is>
           <t>['Preheat the oven to 375°F (190°C).', 'Arrange carrot and beet slices on a baking sheet.', 'Sprinkle with smoked paprika and bake for 20-25 minutes, flipping halfway.']</t>
         </is>
@@ -4947,82 +5182,87 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>VEGAN RANCH VEGGIE CUPS</t>
+          <t>Vegan Ranch Veggie Cups</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t>3629</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>['1 cup chopped vegetables (carrots, celery, bell peppers)', '¼ cup vegan ranch dressing']</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>1. Divide chopped vegetables into two small cups.
 2. Add vegan ranch dressing for dipping.</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>{"calories": 85.0, "protein": 1.0, "carbs": 9.0, "fiber": 3.0, "fat": 5.0}</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H48" t="n">
+      <c r="I48" t="n">
         <v>5</v>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L48" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N48" t="b">
-        <v>0</v>
-      </c>
       <c r="O48" t="b">
+        <v>0</v>
+      </c>
+      <c r="P48" t="b">
         <v>1</v>
       </c>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr">
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr">
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr">
         <is>
           <t>1. Divide chopped vegetables into two small cups.
 2. Add vegan ranch dressing for dipping.</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr">
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr">
         <is>
           <t>['Divide chopped vegetables into two small cups.', 'Add vegan ranch dressing for dipping.']</t>
         </is>
@@ -5041,82 +5281,87 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>APPLE NACHOS WITH ALMOND BUTTER</t>
+          <t>Apple Nachos With Almond Butter</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t>3630</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>['1 apple, sliced thinly', '2 tbsp almond butter', '1 tsp chia seeds']</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>1. Arrange apple slices on a plate.
 2. Drizzle almond butter on top and sprinkle with chia seeds.</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>{"calories": 140.0, "protein": 3.0, "carbs": 20.0, "fiber": 4.0, "fat": 6.0}</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H49" t="n">
+      <c r="I49" t="n">
         <v>5</v>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L49" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N49" t="b">
-        <v>0</v>
-      </c>
       <c r="O49" t="b">
+        <v>0</v>
+      </c>
+      <c r="P49" t="b">
         <v>1</v>
       </c>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr">
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr">
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr">
         <is>
           <t>1. Arrange apple slices on a plate.
 2. Drizzle almond butter on top and sprinkle with chia seeds.</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr">
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr">
         <is>
           <t>['Arrange apple slices on a plate.', 'Drizzle almond butter on top and sprinkle with chia seeds.']</t>
         </is>
@@ -5135,84 +5380,89 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BAKED SPICED CHICKPEAS</t>
+          <t>Baked Spiced Chickpeas</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t>3631</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>['1 can chickpeas, drained and rinsed', '1 tsp smoked paprika', '½ tsp garlic powder']</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 400°F (200°C).
 2. Pat chickpeas dry and toss with smoked paprika and garlic powder.
 3. Spread on a baking sheet and bake for 25-30 minutes until crispy.</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>{"calories": 130.0, "protein": 6.0, "carbs": 22.0, "fiber": 6.0, "fat": 2.0}</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H50" t="n">
+      <c r="I50" t="n">
         <v>30</v>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L50" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N50" t="b">
-        <v>0</v>
-      </c>
       <c r="O50" t="b">
+        <v>0</v>
+      </c>
+      <c r="P50" t="b">
         <v>1</v>
       </c>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr">
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr">
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 400°F (200°C).
 2. Pat chickpeas dry and toss with smoked paprika and garlic powder.
 3. Spread on a baking sheet and bake for 25-30 minutes until crispy.</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr">
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr">
         <is>
           <t>['Preheat the oven to 400°F (200°C).', 'Pat chickpeas dry and toss with smoked paprika and garlic powder.', 'Spread on a baking sheet and bake for 25-30 minutes until crispy.']</t>
         </is>
@@ -5231,82 +5481,87 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AVOCADO RICE CAKES</t>
+          <t>Avocado Rice Cakes</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t>3632</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>['2 rice cakes', '½ avocado, mashed', '1 tsp lemon juice']</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>1. Spread mashed avocado on rice cakes.
 2. Drizzle with lemon juice and serve immediately.</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>{"calories": 120.0, "protein": 2.0, "carbs": 15.0, "fiber": 3.0, "fat": 6.0}</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H51" t="n">
+      <c r="I51" t="n">
         <v>5</v>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L51" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N51" t="b">
-        <v>0</v>
-      </c>
       <c r="O51" t="b">
+        <v>0</v>
+      </c>
+      <c r="P51" t="b">
         <v>1</v>
       </c>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr">
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr">
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr">
         <is>
           <t>1. Spread mashed avocado on rice cakes.
 2. Drizzle with lemon juice and serve immediately.</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr">
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr">
         <is>
           <t>['Spread mashed avocado on rice cakes.', 'Drizzle with lemon juice and serve immediately.']</t>
         </is>
@@ -5325,84 +5580,89 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FROZEN BERRY YOGURT BITES</t>
+          <t>Frozen Berry Yogurt Bites</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t>3633</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>['1 cup unsweetened coconut yogurt', '½ cup mixed berries']</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>1. Divide coconut yogurt into a silicone mold or ice cube tray.
 2. Add a few berries to each section.
 3. Freeze for 1 hour before serving.</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>{"calories": 80.0, "protein": 1.0, "carbs": 13.0, "fiber": 3.0, "fat": 2.0}</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H52" t="n">
+      <c r="I52" t="n">
         <v>10</v>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t>['desserts', 'oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L52" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N52" t="b">
-        <v>0</v>
-      </c>
       <c r="O52" t="b">
+        <v>0</v>
+      </c>
+      <c r="P52" t="b">
         <v>1</v>
       </c>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr">
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr">
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr">
         <is>
           <t>1. Divide coconut yogurt into a silicone mold or ice cube tray.
 2. Add a few berries to each section.
 3. Freeze for 1 hour before serving.</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr">
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr">
         <is>
           <t>['Divide coconut yogurt into a silicone mold or ice cube tray.', 'Add a few berries to each section.', 'Freeze for 1 hour before serving.']</t>
         </is>
@@ -5421,15 +5681,20 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SWEET POTATO BITES WITH TAHINI DRIZZLE</t>
+          <t>Sweet Potato Bites With Tahini Drizzle</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t>3634</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>['1 medium sweet potato, sliced into rounds', '1 tbsp tahini', '1 tsp lemon juice', '¼ tsp smoked paprika']</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 400°F (200°C).
 2. Arrange sweet potato rounds on a baking sheet and bake for 20 minutes.
@@ -5437,61 +5702,61 @@
 4. Drizzle tahini mixture over baked sweet potato rounds and serve.</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>{"calories": 145.0, "protein": 2.0, "carbs": 24.0, "fiber": 4.0, "fat": 4.5}</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H53" t="n">
+      <c r="I53" t="n">
         <v>25</v>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N53" t="b">
-        <v>0</v>
-      </c>
       <c r="O53" t="b">
+        <v>0</v>
+      </c>
+      <c r="P53" t="b">
         <v>1</v>
       </c>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr">
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr">
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 400°F (200°C).
 2. Arrange sweet potato rounds on a baking sheet and bake for 20 minutes.
@@ -5499,8 +5764,8 @@
 4. Drizzle tahini mixture over baked sweet potato rounds and serve.</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr">
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr">
         <is>
           <t>['Preheat the oven to 400°F (200°C).', 'Arrange sweet potato rounds on a baking sheet and bake for 20 minutes.', 'Mix tahini, lemon juice, and smoked paprika in a small bowl.', 'Drizzle tahini mixture over baked sweet potato rounds and serve.']</t>
         </is>
@@ -5519,84 +5784,89 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CAULIFLOWER BUFFALO BITES</t>
+          <t>Cauliflower Buffalo Bites</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t>3635</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>['1 small head cauliflower, cut into florets', '2 tbsp hot sauce', '1 tsp garlic powder']</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 400°F (200°C).
 2. Toss cauliflower florets with hot sauce and garlic powder.
 3. Spread on a baking sheet and bake for 25 minutes, flipping halfway.</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>{"calories": 70.0, "protein": 3.0, "carbs": 15.0, "fiber": 5.0, "fat": 0.0}</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H54" t="n">
+      <c r="I54" t="n">
         <v>30</v>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L54" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N54" t="b">
-        <v>0</v>
-      </c>
       <c r="O54" t="b">
+        <v>0</v>
+      </c>
+      <c r="P54" t="b">
         <v>1</v>
       </c>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr">
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr">
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 400°F (200°C).
 2. Toss cauliflower florets with hot sauce and garlic powder.
 3. Spread on a baking sheet and bake for 25 minutes, flipping halfway.</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr">
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr">
         <is>
           <t>['Preheat the oven to 400°F (200°C).', 'Toss cauliflower florets with hot sauce and garlic powder.', 'Spread on a baking sheet and bake for 25 minutes, flipping halfway.']</t>
         </is>
@@ -5615,84 +5885,89 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ROASTED EDAMAME</t>
+          <t>Roasted Edamame</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t>3636</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>['1 cup frozen shelled edamame, thawed', '1 tsp smoked paprika', 'Salt to taste']</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 375°F (190°C).
 2. Toss edamame with smoked paprika and salt.
 3. Spread on a baking sheet and roast for 15-20 minutes.</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>{"calories": 95.0, "protein": 8.0, "carbs": 8.0, "fiber": 4.0, "fat": 2.5}</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H55" t="n">
+      <c r="I55" t="n">
         <v>20</v>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N55" t="b">
-        <v>0</v>
-      </c>
       <c r="O55" t="b">
+        <v>0</v>
+      </c>
+      <c r="P55" t="b">
         <v>1</v>
       </c>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr">
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr">
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr">
         <is>
           <t>1. Preheat the oven to 375°F (190°C).
 2. Toss edamame with smoked paprika and salt.
 3. Spread on a baking sheet and roast for 15-20 minutes.</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr">
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr">
         <is>
           <t>['Preheat the oven to 375°F (190°C).', 'Toss edamame with smoked paprika and salt.', 'Spread on a baking sheet and roast for 15-20 minutes.']</t>
         </is>
@@ -5711,15 +5986,20 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>VEGAN CHOCOLATE BARK</t>
+          <t>Vegan Chocolate Bark</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t>3637</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>['½ cup vegan dark chocolate chips', '2 tbsp shredded coconut', '1 tbsp chopped almonds']</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>1. Melt chocolate chips in the microwave or a double boiler.
 2. Spread melted chocolate on parchment paper.
@@ -5727,61 +6007,61 @@
 4. Chill in the fridge for 30 minutes before breaking into pieces.</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>{"calories": 120.0, "protein": 2.0, "carbs": 10.0, "fiber": 2.0, "fat": 8.0}</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>4 servings</t>
         </is>
       </c>
-      <c r="H56" t="n">
+      <c r="I56" t="n">
         <v>10</v>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t>['desserts', 'oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N56" t="b">
-        <v>0</v>
-      </c>
       <c r="O56" t="b">
+        <v>0</v>
+      </c>
+      <c r="P56" t="b">
         <v>1</v>
       </c>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr">
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr">
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr">
         <is>
           <t>1. Melt chocolate chips in the microwave or a double boiler.
 2. Spread melted chocolate on parchment paper.
@@ -5789,8 +6069,8 @@
 4. Chill in the fridge for 30 minutes before breaking into pieces.</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr">
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr">
         <is>
           <t>['Melt chocolate chips in the microwave or a double boiler.', 'Spread melted chocolate on parchment paper.', 'Sprinkle with coconut and almonds.', 'Chill in the fridge for 30 minutes before breaking into pieces.']</t>
         </is>
@@ -5809,84 +6089,89 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>VEGAN DEVILED POTATOES</t>
+          <t>Vegan Deviled Potatoes</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t>3638</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>['4 small baby potatoes, boiled and halved', '2 tbsp hummus', '1 tsp smoked paprika']</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>1. Scoop out a small portion of the potato centers.
 2. Fill the hollow with hummus.
 3. Sprinkle with smoked paprika and serve.</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>{"calories": 75.0, "protein": 2.0, "carbs": 15.0, "fiber": 2.0, "fat": 1.0}</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>2 servings</t>
         </is>
       </c>
-      <c r="H57" t="n">
+      <c r="I57" t="n">
         <v>15</v>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'plant-based', 'whole-foods', 'vegan', 'oil-free', 'snacks', 'desserts', 'smoothies/shakes']</t>
-        </is>
-      </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t>['oil-free', 'plant-based', 'snacks', 'vegan', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>plant_based</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
         <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
           <t>Sweet</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N57" t="b">
-        <v>0</v>
-      </c>
       <c r="O57" t="b">
+        <v>0</v>
+      </c>
+      <c r="P57" t="b">
         <v>1</v>
       </c>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr">
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr">
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr">
         <is>
           <t>1. Scoop out a small portion of the potato centers.
 2. Fill the hollow with hummus.
 3. Sprinkle with smoked paprika and serve.</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr">
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr">
         <is>
           <t>['Scoop out a small portion of the potato centers.', 'Fill the hollow with hummus.', 'Sprinkle with smoked paprika and serve.']</t>
         </is>
